--- a/archive/2026/2026-10-27.xlsx
+++ b/archive/2026/2026-10-27.xlsx
@@ -14,11 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_外資_上櫃" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_投信_上櫃" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="富邦 e_自營商_上櫃" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_外資_上市" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_投信_上市" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_自營商_上市" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="證交所_三大法人合計_上市" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2875,3654 +2871,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市自營商買賣超排行｜2026-10-27｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00664R</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>31667</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-853675</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00632R</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>元大台灣50反1</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>23758</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-110058</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00680L</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>元大美債20正2</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>14743</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-65837</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>11404</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-60812</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>10430</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-47036</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>7976</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-46086</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>00637L</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>元大滬深300正2</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>6584</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-40774</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>6290</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-29384</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>4426</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-17555</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>4224</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00673R</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P原油反1</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-16453</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>2162</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00415A</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>主動群益核心50</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-16074</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>00642U</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P石油</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1926</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-15561</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>1907</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-15484</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>主動野村台灣50</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1873</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-12999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>00988A</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>主動統一全球創新</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>1807</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-12302</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1754</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-9598</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>1687</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-8882</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1678</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-8325</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>00665L</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>富邦恒生國企正2</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>1651</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-8195</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>1635</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-7430</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>00753L</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>中信中國50正2</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1609</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-6372</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1604</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00922</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>國泰台灣領袖50</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-6272</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>00693U</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>期街口S&amp;P黃豆</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1596</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-6181</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1579</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-4798</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>00946</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>群益科技高息成長</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1563</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-4763</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1552</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>00996A</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>主動兆豐台灣豐收</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-4721</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>00683L</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>期元大美元指正2</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>1379</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-4685</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>1357</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>009821</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>野村稀土關鍵資源</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-4546</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>00402A</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>主動安聯美國科技</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1339</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-3398</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1324</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-3348</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>00715L</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>期街口布蘭特正2</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>1272</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>006208</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-3305</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1216</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>00662</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>富邦NASDAQ</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-3269</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>1175</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>009827</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>玉山未來全球算力</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-3201</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>1037</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-2775</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>1006</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-2614</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>00671R</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>富邦NASDAQ反1</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>982</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00635U</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P黃金</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-2293</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>00686R</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>群益臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>895</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>00708L</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P黃金正2</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-2152</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>866</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>00896</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>中信綠能及電動車</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-2116</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>847</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00738U</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>期元大道瓊白銀</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-2106</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>815</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-2015</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>807</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>00980A</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>主動野村臺灣優選</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-1896</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>00994A</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>主動第一金台股優</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>00923</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>群益台ESG低碳50</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-1509</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>009824</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>群益美國科技巨頭</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>686</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>00999A</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>主動野村臺灣高息</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-1425</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>00712</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>復華富時不動產</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>684</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>00984D</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>主動聯博全球非投</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-1396</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>665</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>009803</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>玉山市值動能50</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-1312</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>664</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>00408A</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>主動第一金優股息</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-1284</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>645</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>00646</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>元大S&amp;P500</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-1228</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>00982D</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>主動富邦動態入息</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>640</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>00954</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>中信日本半導體</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-1139</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>633</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>群創</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-1133</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>00945B</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>凱基美國非投等債</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>603</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>009826</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>貝萊德世界股票</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-980</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市三大法人合計買賣超排行｜2026-10-27｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>62636</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-921902</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00664R</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>國泰臺灣加權反1</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>31765</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-165772</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>30084</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-132732</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>23864</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-95215</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>00632R</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>元大台灣50反1</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>23501</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-69796</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>00712</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>復華富時不動產</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>18660</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>00685L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>群益臺灣加權正2</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-60273</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>17762</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-59224</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>14154</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-43542</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>00680L</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>元大美債20正2</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>14034</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-37220</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>12923</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-31223</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>12917</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-28828</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>12799</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>00415A</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>主動群益核心50</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-24596</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>00918</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>大華優利高填息30</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>12110</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-22115</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>11257</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>00673R</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>期元大S&amp;P原油反1</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-16452</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>10965</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>00412A</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>主動安聯亞半導體</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-16020</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>東台</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>9985</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-15580</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>00637L</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>元大滬深300正2</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>8858</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>主動富邦台灣龍耀</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-14413</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>00961</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>FT臺灣永續高息</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>8734</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-13448</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>8488</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-11314</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>8455</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-9282</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>8370</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00409A</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>主動復華全球50</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-9154</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>上曜</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>7553</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-9138</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>7124</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-8932</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>6879</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-8340</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>6299</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>00891</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>中信關鍵半導體</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-8181</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>6074</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-7118</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>6023</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>00922</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>國泰台灣領袖50</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-7040</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>6023</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>主動群益台灣強棒</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-6664</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>潤隆</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>5961</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-6192</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>5876</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>00927</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>群益半導體收益</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-6111</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>5688</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-5947</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>5572</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-5624</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>5162</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>009821</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>野村稀土關鍵資源</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-5446</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>4997</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-5249</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>4973</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>006208</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-4840</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>4891</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>00996A</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>主動兆豐台灣豐收</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-4730</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>4832</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-4507</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>00900</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>富邦特選高股息30</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>4789</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>00662</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>富邦NASDAQ</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-3343</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>4721</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>009827</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>玉山未來全球算力</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-3206</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>4537</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-3149</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>4439</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>00909</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>國泰數位支付服務</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-3100</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>4268</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>臺企銀</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-2969</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>00988A</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>主動統一全球創新</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>3956</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>中工</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-2840</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>晶豪科</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>3884</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>新纖</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-2751</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>3552</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>新興</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-2717</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>6919</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>康霈*</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>3510</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>GIS-KY</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-2709</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>國產</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>3391</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6269</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>台郡</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-2693</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>00940</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>元大台灣價值高息</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>3365</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-2662</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>3326</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>群益證</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-2624</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>3293</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>00980A</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>主動野村臺灣優選</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-2233</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>本檔由程式自動抓取公開網頁整理，僅供參考，不構成投資建議。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>顏色慣例：紅色＝買超／上漲，綠色＝賣超／下跌。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19955,3613 +16303,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市外資買賣超排行｜2026-10-27｜單位：張</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>本檔由程式自動抓取公開網頁整理，僅供參考，不構成投資建議。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>56012</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-95960</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>29598</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00406A</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>主動中信台灣收益</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-68228</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>22489</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00981A</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>主動統一台股增長</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-66895</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>00712</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>復華富時不動產</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>17976</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>主動統一升級50</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-55714</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>16601</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-28421</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>宏碁</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>12810</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>009828</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>中信台日韓PCB</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-24919</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>11566</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-14090</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>10719</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>主動群益科技創新</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-13267</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>東台</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>9879</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>主動國泰動能高息</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-13233</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>009829</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>大華韓國KOSPI50</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>9211</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>009816</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>凱基台灣TOP50</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-12187</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>9102</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-11968</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>8645</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-10864</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>8081</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-8895</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上曜</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>7547</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>00415A</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>主動群益核心50</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-8522</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>7216</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-6288</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>6599</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-5362</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>潤隆</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>6559</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-5281</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>6058</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>00881</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>國泰台灣科技龍頭</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-4340</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>5809</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-3334</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>5768</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>新興</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-3265</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>5464</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>臺企銀</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-2979</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>5328</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>00909</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>國泰數位支付服務</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-2937</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>統一</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>5178</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6269</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>台郡</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-2901</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>台塑</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>4994</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-2867</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>4972</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>中工</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-2840</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>4916</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6213</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>聯茂</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-2825</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>4801</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>00631L</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>元大台灣50正2</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-2768</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>4728</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1409</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>新纖</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-2758</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3702</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>大聯大</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>4700</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>群益證</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-2615</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>00929</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>復華台灣科技優息</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>4107</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6456</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>GIS-KY</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-2432</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>00830</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>國泰費城半導體</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-2354</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>3957</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-2339</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>00953B</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>群益優選非投等債</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>3933</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-2301</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>3698</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-2283</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>3613</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0052</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>富邦科技</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-2276</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>晶豪科</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>3560</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4989</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>榮科</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-2143</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>6919</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>康霈*</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>3503</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>中環</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-2024</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>國產</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>3381</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-1880</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>3302</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>主動凱基台灣</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-1839</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>5871</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>中租-KY</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>3020</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3056</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>富華新</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-1762</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>和益</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>2929</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>信邦</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-1724</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>上銀</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>2547</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>國泰永續高股息</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-1716</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>00919</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>群益台灣精選高息</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>2487</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-1618</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>和碩</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>2462</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>00688L</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>國泰20年美債正2</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-1569</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>00997A</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>主動群益美國增長</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>2318</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>定穎投控</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-1567</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>2284</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>006208</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>富邦台50</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-1564</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>00637L</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>元大滬深300正2</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>2274</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-1539</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>9910</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>豐泰</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>2185</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>主動復華未來50</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-1507</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>微星</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>2174</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6116</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>彩晶</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-1499</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>00988A</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>主動統一全球創新</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>2149</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-1426</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>證交所｜上市投信買賣超排行｜2026-10-27｜單位：張</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>買超</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>賣超</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>買超(張)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>名次</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>賣超(張)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>收盤價</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>漲跌</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>力積電</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>4937</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2886</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>兆豐金</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>-4555</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>元大台灣50</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>4710</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>-2773</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2883</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>凱基金</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>4145</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-2722</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>3786</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>華航</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>-2287</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>友達</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>3520</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>貿聯-KY</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>-1190</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>台泥</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>2800</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>-1093</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>玉山金</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>2717</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>彰銀</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>-638</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>2420</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>崇越</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>-534</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>華新科</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>2103</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>中纖</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>-528</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>2092</v>
-      </c>
-      <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>禾伸堂</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-492</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>台化</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>中信金</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>-481</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>永豐金</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1964</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>和桐</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>-471</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>1879</v>
-      </c>
-      <c r="H16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>力麗</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="n">
-        <v>-419</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2352</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>佳世達</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1577</v>
-      </c>
-      <c r="H17" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>9921</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>巨大</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>1525</v>
-      </c>
-      <c r="H18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>漢翔</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>-325</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2887</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>台新新光金</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1394</v>
-      </c>
-      <c r="H19" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-318</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>1391</v>
-      </c>
-      <c r="H20" t="n">
-        <v>17</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>力鵬</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>-314</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>第一金</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1274</v>
-      </c>
-      <c r="H21" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-303</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>台玻</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>1124</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3034</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>聯詠</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-294</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>8070</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>長華*</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>1120</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>-288</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1113</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5469</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>瀚宇博</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-286</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>合庫金</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1043</v>
-      </c>
-      <c r="H25" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>文曄</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>-280</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>969</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>台灣高鐵</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>-253</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>906</v>
-      </c>
-      <c r="H27" t="n">
-        <v>24</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>亞泥</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>華南金</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>872</v>
-      </c>
-      <c r="H28" t="n">
-        <v>25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>興富發</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-199</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>830</v>
-      </c>
-      <c r="H29" t="n">
-        <v>26</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>-178</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>828</v>
-      </c>
-      <c r="H30" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>國碩</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-176</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>793</v>
-      </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5269</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>祥碩</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-149</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>744</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>上海商銀</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>-146</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>681</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>辛耘</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-127</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>675</v>
-      </c>
-      <c r="H34" t="n">
-        <v>31</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>東鹼</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-116</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>648</v>
-      </c>
-      <c r="H35" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3706</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>神達</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-102</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>00980A</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>主動野村臺灣優選</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>644</v>
-      </c>
-      <c r="H36" t="n">
-        <v>33</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>勤誠</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>590</v>
-      </c>
-      <c r="H37" t="n">
-        <v>34</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>正新</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>-98</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>582</v>
-      </c>
-      <c r="H38" t="n">
-        <v>35</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>日電貿</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-96</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>542</v>
-      </c>
-      <c r="H39" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>9946</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>三發地產</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>-79</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>491</v>
-      </c>
-      <c r="H40" t="n">
-        <v>37</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2316</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>楠梓電</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>-79</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>470</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>希華</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>-77</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>可成</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>468</v>
-      </c>
-      <c r="H42" t="n">
-        <v>39</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1515</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>力山</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-77</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>0056</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>元大高股息</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>寶成</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>-76</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>富邦金</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>395</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8033</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>雷虎</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-76</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>6257</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>矽格</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>378</v>
-      </c>
-      <c r="H45" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>矽力*-KY</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-75</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>375</v>
-      </c>
-      <c r="H46" t="n">
-        <v>43</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2347</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>聯強</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-74</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>國泰金</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>372</v>
-      </c>
-      <c r="H47" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3060</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>銘異</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-73</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2845</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>遠東銀</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>363</v>
-      </c>
-      <c r="H48" t="n">
-        <v>45</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>6526</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>達發</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-72</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>00935</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>野村臺灣新科技50</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>317</v>
-      </c>
-      <c r="H49" t="n">
-        <v>46</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-70</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>信邦</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>311</v>
-      </c>
-      <c r="H50" t="n">
-        <v>47</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3015</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>全漢</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>-70</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2478</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>大毅</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-66</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>308</v>
-      </c>
-      <c r="H52" t="n">
-        <v>49</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8476</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>台境*</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>南茂</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>304</v>
-      </c>
-      <c r="H53" t="n">
-        <v>50</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>凱美</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-53</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>顏色慣例：紅色＝買超／上漲，綠色＝賣超／下跌。</t>
+        </is>
       </c>
     </row>
   </sheetData>
